--- a/Documentation/F25/BOM.xlsx
+++ b/Documentation/F25/BOM.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juxin\Documents\MIDI-Projects\Documentation\F25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8497C883-49FE-42CF-9594-6856A6334935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94788670-424E-4AA4-A31D-0A9A16703FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A83A8560-5CBD-4349-BA30-694DDB52E494}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A83A8560-5CBD-4349-BA30-694DDB52E494}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Print1" sheetId="2" r:id="rId2"/>
+    <sheet name="Print2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="186">
   <si>
     <t>Category</t>
   </si>
@@ -434,9 +436,6 @@
     <t>Solenoid, 25N</t>
   </si>
   <si>
-    <t>Solenoid, 15N</t>
-  </si>
-  <si>
     <t>Bass Guitar</t>
   </si>
   <si>
@@ -570,6 +569,33 @@
   </si>
   <si>
     <t>Hours</t>
+  </si>
+  <si>
+    <t>Solenoid, 5N</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/JF-0530B-gangbei-0530B-Electromagnet-keepping-Solenoid/dp/B07V3JRDLJ?th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> B07V3JRDLJ</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/AARTERZZA-JF-1039B-Push-Pull-Solenoid-Electromagnet/dp/B0DJVL6MHG?th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Yaocom-European-Standard-Aluminum-Extrusion/dp/B0DX7B5ZNN/ref=sr_1_3?dib=eyJ2IjoiMSJ9.dnPBW5BnGWFI7alZa4I2U-eVIo5GXTpxHJ9tQMCOqZxXMZPrh3lK9sBZdB6eNKI7a_ZoQK8DljT8j86EjeJB-TgIjBv-7rR1aWPd3Za75LvZ6xV36SRWb3nkD_9LcJV4SBCgqPJvykjxeW4zMrXNekWu9XvrzbX6PY3tsirpeNhu1zFpZ2WD0UqR3vN_whM5FQffhRQ2tPdUu8WPP_oVwzEKxtiEkEmALW8h0yRnwVY.X_WCrDJoZ7GpA7NadGh_qshU4Mp-sX0PWu2dVc1ia4c&amp;dib_tag=se&amp;keywords=m5%2B2020%2Bnut&amp;qid=1766005804&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>B0DJVL6MHG</t>
+  </si>
+  <si>
+    <t>All PCB</t>
+  </si>
+  <si>
+    <t>Page 89</t>
+  </si>
+  <si>
+    <t>Page 90</t>
   </si>
 </sst>
 </file>
@@ -726,24 +752,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -761,6 +775,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -768,9 +812,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -782,11 +823,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1130,11 +1180,11 @@
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
     <col min="4" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="8"/>
-    <col min="8" max="8" width="9.140625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="4"/>
+    <col min="8" max="8" width="9.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="4" customWidth="1"/>
     <col min="10" max="14" width="9.140625" style="1"/>
-    <col min="15" max="15" width="9.140625" style="11"/>
+    <col min="15" max="15" width="9.140625" style="7"/>
     <col min="16" max="19" width="9.140625" style="1"/>
     <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="1"/>
@@ -1144,35 +1194,35 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="4" t="s">
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="6"/>
+      <c r="N1" s="17"/>
       <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
@@ -1181,41 +1231,39 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="2">
         <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="3">
         <v>0.2</v>
       </c>
-      <c r="H2" s="7">
-        <f>G2*E2</f>
+      <c r="H2" s="3">
+        <f t="shared" ref="H2:H9" si="0">G2*E2</f>
         <v>5.4</v>
       </c>
-      <c r="I2" s="7">
-        <f>H2*100</f>
+      <c r="I2" s="3">
+        <f t="shared" ref="I2:I9" si="1">H2*100</f>
         <v>540</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="9" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="P2" s="1" t="s">
@@ -1223,39 +1271,39 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="2">
         <v>37</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="3">
         <v>0.91</v>
       </c>
-      <c r="H3" s="7">
-        <f>G3*E3</f>
+      <c r="H3" s="3">
+        <f t="shared" si="0"/>
         <v>33.67</v>
       </c>
-      <c r="I3" s="7">
-        <f>H3*100</f>
+      <c r="I3" s="3">
+        <f t="shared" si="1"/>
         <v>3367</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="4" t="s">
+      <c r="K3" s="16"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="9" t="s">
+      <c r="N3" s="17"/>
+      <c r="O3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -1263,39 +1311,39 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="2">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="3">
         <v>2.83</v>
       </c>
-      <c r="H4" s="7">
-        <f>G4*E4</f>
+      <c r="H4" s="3">
+        <f t="shared" si="0"/>
         <v>11.32</v>
       </c>
-      <c r="I4" s="7">
-        <f>H4*100</f>
+      <c r="I4" s="3">
+        <f t="shared" si="1"/>
         <v>1132</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="4" t="s">
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="9" t="s">
+      <c r="N4" s="17"/>
+      <c r="O4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="P4" s="1" t="s">
@@ -1303,39 +1351,39 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
       <c r="E5" s="2">
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="3">
         <v>1.02</v>
       </c>
-      <c r="H5" s="7">
-        <f>G5*E5</f>
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
         <v>8.16</v>
       </c>
-      <c r="I5" s="7">
-        <f>H5*100</f>
+      <c r="I5" s="3">
+        <f t="shared" si="1"/>
         <v>816</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="4" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="9" t="s">
+      <c r="N5" s="17"/>
+      <c r="O5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P5" s="1" t="s">
@@ -1343,39 +1391,39 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
       <c r="E6" s="2">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="3">
         <v>4.9800000000000004</v>
       </c>
-      <c r="H6" s="7">
-        <f>G6*E6</f>
+      <c r="H6" s="3">
+        <f t="shared" si="0"/>
         <v>19.920000000000002</v>
       </c>
-      <c r="I6" s="7">
-        <f>H6*100</f>
+      <c r="I6" s="3">
+        <f t="shared" si="1"/>
         <v>1992.0000000000002</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="4" t="s">
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="9" t="s">
+      <c r="N6" s="17"/>
+      <c r="O6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="1" t="s">
@@ -1383,39 +1431,39 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
       <c r="E7" s="2">
         <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="3">
         <v>1.67</v>
       </c>
-      <c r="H7" s="7">
-        <f>G7*E7</f>
+      <c r="H7" s="3">
+        <f t="shared" si="0"/>
         <v>88.509999999999991</v>
       </c>
-      <c r="I7" s="7">
-        <f>H7*100</f>
+      <c r="I7" s="3">
+        <f t="shared" si="1"/>
         <v>8851</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4" t="s">
+      <c r="K7" s="16"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="9" t="s">
+      <c r="N7" s="17"/>
+      <c r="O7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="1" t="s">
@@ -1423,39 +1471,39 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="2">
         <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="3">
         <v>0.33</v>
       </c>
-      <c r="H8" s="7">
-        <f>G8*E8</f>
+      <c r="H8" s="3">
+        <f t="shared" si="0"/>
         <v>3.96</v>
       </c>
-      <c r="I8" s="7">
-        <f>H8*100</f>
+      <c r="I8" s="3">
+        <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="4" t="s">
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="9" t="s">
+      <c r="N8" s="17"/>
+      <c r="O8" s="5" t="s">
         <v>40</v>
       </c>
       <c r="P8" s="1" t="s">
@@ -1463,39 +1511,39 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
       <c r="E9" s="2">
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="3">
         <v>0.34</v>
       </c>
-      <c r="H9" s="7">
-        <f>G9*E9</f>
+      <c r="H9" s="3">
+        <f t="shared" si="0"/>
         <v>15.64</v>
       </c>
-      <c r="I9" s="7">
-        <f>H9*100</f>
+      <c r="I9" s="3">
+        <f t="shared" si="1"/>
         <v>1564</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="4" t="s">
+      <c r="K9" s="16"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="9" t="s">
+      <c r="N9" s="17"/>
+      <c r="O9" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P9" s="1" t="s">
@@ -1503,39 +1551,39 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
       <c r="E10" s="2">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="3">
         <v>3.69</v>
       </c>
-      <c r="H10" s="7">
-        <f t="shared" ref="H10:H15" si="0">G10*E10</f>
+      <c r="H10" s="3">
+        <f t="shared" ref="H10:H14" si="2">G10*E10</f>
         <v>51.66</v>
       </c>
-      <c r="I10" s="7">
-        <f t="shared" ref="I10:I31" si="1">H10*100</f>
+      <c r="I10" s="3">
+        <f t="shared" ref="I10:I30" si="3">H10*100</f>
         <v>5166</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="4" t="s">
+      <c r="K10" s="16"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="9" t="s">
+      <c r="N10" s="17"/>
+      <c r="O10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="P10" s="1" t="s">
@@ -1543,39 +1591,39 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
       <c r="E11" s="2">
         <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="3">
         <v>0.54</v>
       </c>
-      <c r="H11" s="7">
-        <f t="shared" si="0"/>
+      <c r="H11" s="3">
+        <f t="shared" si="2"/>
         <v>6.48</v>
       </c>
-      <c r="I11" s="7">
-        <f t="shared" si="1"/>
+      <c r="I11" s="3">
+        <f t="shared" si="3"/>
         <v>648</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="4" t="s">
+      <c r="K11" s="16"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="9" t="s">
+      <c r="N11" s="17"/>
+      <c r="O11" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P11" s="1" t="s">
@@ -1583,39 +1631,39 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
       <c r="E12" s="2">
         <v>188</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="3">
         <v>0.1</v>
       </c>
-      <c r="H12" s="7">
-        <f t="shared" si="0"/>
+      <c r="H12" s="3">
+        <f t="shared" si="2"/>
         <v>18.8</v>
       </c>
-      <c r="I12" s="7">
-        <f t="shared" si="1"/>
+      <c r="I12" s="3">
+        <f t="shared" si="3"/>
         <v>1880</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="4" t="s">
+      <c r="K12" s="16"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="9" t="s">
+      <c r="N12" s="17"/>
+      <c r="O12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="P12" s="1" t="s">
@@ -1623,39 +1671,39 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="2">
         <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="3">
         <v>0.1</v>
       </c>
-      <c r="H13" s="7">
-        <f t="shared" si="0"/>
+      <c r="H13" s="3">
+        <f t="shared" si="2"/>
         <v>2.4000000000000004</v>
       </c>
-      <c r="I13" s="7">
-        <f t="shared" si="1"/>
+      <c r="I13" s="3">
+        <f t="shared" si="3"/>
         <v>240.00000000000003</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="4" t="s">
+      <c r="K13" s="16"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="9" t="s">
+      <c r="N13" s="17"/>
+      <c r="O13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="P13" s="1" t="s">
@@ -1663,39 +1711,39 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
       <c r="E14" s="2">
         <v>3</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H14" s="7">
-        <f t="shared" si="0"/>
+      <c r="H14" s="3">
+        <f t="shared" si="2"/>
         <v>0.86999999999999988</v>
       </c>
-      <c r="I14" s="7">
-        <f t="shared" si="1"/>
+      <c r="I14" s="3">
+        <f t="shared" si="3"/>
         <v>86.999999999999986</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="4" t="s">
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="9" t="s">
+      <c r="N14" s="17"/>
+      <c r="O14" s="5" t="s">
         <v>54</v>
       </c>
       <c r="P14" s="1" t="s">
@@ -1703,39 +1751,39 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
       <c r="E15" s="2">
         <v>28</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="3">
         <v>4.51</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="3">
         <f>G15</f>
         <v>4.51</v>
       </c>
-      <c r="I15" s="7">
-        <f t="shared" si="1"/>
+      <c r="I15" s="3">
+        <f t="shared" si="3"/>
         <v>451</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="4" t="s">
+      <c r="K15" s="16"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="9" t="s">
+      <c r="N15" s="17"/>
+      <c r="O15" s="5" t="s">
         <v>58</v>
       </c>
       <c r="P15" s="1" t="s">
@@ -1743,39 +1791,41 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="2">
         <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="3">
         <v>5.87</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="3">
         <f>G16*E16</f>
         <v>46.96</v>
       </c>
-      <c r="I16" s="7">
-        <f t="shared" si="1"/>
+      <c r="I16" s="3">
+        <f t="shared" si="3"/>
         <v>4696</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="4" t="s">
+      <c r="K16" s="16"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="6"/>
-      <c r="O16" s="9" t="s">
+      <c r="N16" s="17"/>
+      <c r="O16" s="5" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="1" t="s">
@@ -1783,39 +1833,39 @@
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
       <c r="E17" s="2">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="3">
         <v>0.33</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="3">
         <f>G17*E17</f>
         <v>1.6500000000000001</v>
       </c>
-      <c r="I17" s="7">
-        <f t="shared" si="1"/>
+      <c r="I17" s="3">
+        <f t="shared" si="3"/>
         <v>165</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="4" t="s">
+      <c r="K17" s="16"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="9" t="s">
+      <c r="N17" s="17"/>
+      <c r="O17" s="5" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="1" t="s">
@@ -1823,39 +1873,39 @@
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
       <c r="E18" s="2">
         <v>4</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="3">
         <v>4.28</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="3">
         <f>G18*E18</f>
         <v>17.12</v>
       </c>
-      <c r="I18" s="7">
-        <f t="shared" si="1"/>
+      <c r="I18" s="3">
+        <f t="shared" si="3"/>
         <v>1712</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="4" t="s">
+      <c r="K18" s="16"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="9" t="s">
+      <c r="N18" s="17"/>
+      <c r="O18" s="5" t="s">
         <v>66</v>
       </c>
       <c r="P18" s="1" t="s">
@@ -1863,39 +1913,39 @@
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
       <c r="E19" s="2">
         <v>48</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="3">
         <v>0.25</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="3">
         <f>G19*E19</f>
         <v>12</v>
       </c>
-      <c r="I19" s="7">
-        <f t="shared" si="1"/>
+      <c r="I19" s="3">
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="4" t="s">
+      <c r="K19" s="16"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="9" t="s">
+      <c r="N19" s="17"/>
+      <c r="O19" s="5" t="s">
         <v>81</v>
       </c>
       <c r="P19" s="1" t="s">
@@ -1903,39 +1953,39 @@
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="12"/>
+      <c r="B20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
       <c r="E20" s="2">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="3">
         <v>2.4300000000000002</v>
       </c>
-      <c r="H20" s="7">
-        <f t="shared" ref="H20:H37" si="2">G20*E20</f>
+      <c r="H20" s="3">
+        <f t="shared" ref="H20:H36" si="4">G20*E20</f>
         <v>2.4300000000000002</v>
       </c>
-      <c r="I20" s="7">
-        <f t="shared" si="1"/>
+      <c r="I20" s="3">
+        <f t="shared" si="3"/>
         <v>243.00000000000003</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="4" t="s">
+      <c r="K20" s="16"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="9" t="s">
+      <c r="N20" s="17"/>
+      <c r="O20" s="5" t="s">
         <v>74</v>
       </c>
       <c r="P20" s="1" t="s">
@@ -1943,39 +1993,39 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
       <c r="E21" s="2">
         <v>6</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="3">
         <v>0.1</v>
       </c>
-      <c r="H21" s="7">
-        <f t="shared" si="2"/>
+      <c r="H21" s="3">
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="I21" s="7">
-        <f t="shared" si="1"/>
+      <c r="I21" s="3">
+        <f t="shared" si="3"/>
         <v>60.000000000000007</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="4" t="s">
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="9" t="s">
+      <c r="N21" s="17"/>
+      <c r="O21" s="5" t="s">
         <v>80</v>
       </c>
       <c r="P21" s="1" t="s">
@@ -1983,39 +2033,39 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
       <c r="E22" s="2">
         <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="3">
         <v>0.49</v>
       </c>
-      <c r="H22" s="7">
-        <f t="shared" si="2"/>
+      <c r="H22" s="3">
+        <f t="shared" si="4"/>
         <v>1.96</v>
       </c>
-      <c r="I22" s="7">
-        <f t="shared" si="1"/>
+      <c r="I22" s="3">
+        <f t="shared" si="3"/>
         <v>196</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="4" t="s">
+      <c r="K22" s="16"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="9" t="s">
+      <c r="N22" s="17"/>
+      <c r="O22" s="5" t="s">
         <v>78</v>
       </c>
       <c r="P22" s="1" t="s">
@@ -2023,130 +2073,130 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="12"/>
+      <c r="B23" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
       <c r="E23" s="2">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="3">
         <v>2.5299999999999998</v>
       </c>
-      <c r="H23" s="7">
-        <f t="shared" si="2"/>
+      <c r="H23" s="3">
+        <f t="shared" si="4"/>
         <v>2.5299999999999998</v>
       </c>
-      <c r="I23" s="7">
-        <f t="shared" si="1"/>
+      <c r="I23" s="3">
+        <f t="shared" si="3"/>
         <v>252.99999999999997</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="4" t="s">
+      <c r="K23" s="16"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="9" t="s">
+      <c r="N23" s="17"/>
+      <c r="O23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="T23" s="3"/>
+      <c r="T23" s="14"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="12"/>
+      <c r="B24" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
       <c r="E24" s="2">
         <v>24</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="3">
         <v>1.75</v>
       </c>
-      <c r="H24" s="7">
-        <f t="shared" si="2"/>
+      <c r="H24" s="3">
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="I24" s="7">
-        <f t="shared" si="1"/>
+      <c r="I24" s="3">
+        <f t="shared" si="3"/>
         <v>4200</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="4" t="s">
+      <c r="K24" s="16"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="9" t="s">
+      <c r="N24" s="17"/>
+      <c r="O24" s="5" t="s">
         <v>85</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S24" s="19" t="s">
+      <c r="S24" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="T24" s="7">
+      <c r="T24" s="3">
         <f>SUM(H2:H35)</f>
         <v>583.96999999999991</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="12"/>
+      <c r="B25" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
       <c r="E25" s="2">
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="3">
         <v>2.35</v>
       </c>
-      <c r="H25" s="7">
-        <f t="shared" si="2"/>
+      <c r="H25" s="3">
+        <f t="shared" si="4"/>
         <v>4.7</v>
       </c>
-      <c r="I25" s="7">
-        <f t="shared" si="1"/>
+      <c r="I25" s="3">
+        <f t="shared" si="3"/>
         <v>470</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="4" t="s">
+      <c r="K25" s="16"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="9" t="s">
+      <c r="N25" s="17"/>
+      <c r="O25" s="5" t="s">
         <v>88</v>
       </c>
       <c r="P25" s="1" t="s">
@@ -2155,45 +2205,45 @@
       <c r="S25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="T25" s="7">
+      <c r="T25" s="3">
         <f>SUM(H36:H51)</f>
-        <v>685.73</v>
+        <v>1440.5299999999997</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="12"/>
+      <c r="B26" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
       <c r="E26" s="2">
         <v>3</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="3">
         <v>0.31</v>
       </c>
-      <c r="H26" s="7">
-        <f t="shared" si="2"/>
+      <c r="H26" s="3">
+        <f t="shared" si="4"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="I26" s="7">
-        <f t="shared" si="1"/>
+      <c r="I26" s="3">
+        <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="4" t="s">
+      <c r="K26" s="16"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="9" t="s">
+      <c r="N26" s="17"/>
+      <c r="O26" s="5" t="s">
         <v>92</v>
       </c>
       <c r="P26" s="1" t="s">
@@ -2202,45 +2252,45 @@
       <c r="S26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T26" s="7">
+      <c r="T26" s="3">
         <f>SUM(H52:H55)</f>
-        <v>22600</v>
+        <v>21400</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="12"/>
+      <c r="B27" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
       <c r="E27" s="2">
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="3">
         <v>0.59</v>
       </c>
-      <c r="H27" s="7">
-        <f t="shared" si="2"/>
+      <c r="H27" s="3">
+        <f t="shared" si="4"/>
         <v>1.18</v>
       </c>
-      <c r="I27" s="7">
-        <f t="shared" si="1"/>
+      <c r="I27" s="3">
+        <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="4" t="s">
+      <c r="K27" s="16"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="9" t="s">
+      <c r="N27" s="17"/>
+      <c r="O27" s="5" t="s">
         <v>94</v>
       </c>
       <c r="P27" s="1" t="s">
@@ -2249,42 +2299,45 @@
       <c r="S27" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="T27" s="2"/>
+      <c r="T27" s="3">
+        <f>SUM(T24:T26)</f>
+        <v>23424.5</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="12"/>
+      <c r="B28" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
       <c r="E28" s="2">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="3">
         <v>3.45</v>
       </c>
-      <c r="H28" s="7">
-        <f t="shared" si="2"/>
+      <c r="H28" s="3">
+        <f t="shared" si="4"/>
         <v>3.45</v>
       </c>
-      <c r="I28" s="7">
-        <f t="shared" si="1"/>
+      <c r="I28" s="3">
+        <f t="shared" si="3"/>
         <v>345</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="K28" s="13"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="4" t="s">
+      <c r="K28" s="19"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="9" t="s">
+      <c r="N28" s="17"/>
+      <c r="O28" s="5" t="s">
         <v>97</v>
       </c>
       <c r="P28" s="1" t="s">
@@ -2292,39 +2345,39 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
       <c r="E29" s="2">
         <v>6</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H29" s="7">
-        <f t="shared" si="2"/>
+      <c r="H29" s="3">
+        <f t="shared" si="4"/>
         <v>6.6000000000000005</v>
       </c>
-      <c r="I29" s="7">
-        <f t="shared" si="1"/>
+      <c r="I29" s="3">
+        <f t="shared" si="3"/>
         <v>660</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="4" t="s">
+      <c r="K29" s="16"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="9" t="s">
+      <c r="N29" s="17"/>
+      <c r="O29" s="5" t="s">
         <v>100</v>
       </c>
       <c r="P29" s="1" t="s">
@@ -2332,39 +2385,39 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
       <c r="E30" s="2">
         <v>3</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="3">
         <v>2.63</v>
       </c>
-      <c r="H30" s="7">
-        <f t="shared" si="2"/>
+      <c r="H30" s="3">
+        <f t="shared" si="4"/>
         <v>7.89</v>
       </c>
-      <c r="I30" s="7">
-        <f t="shared" si="1"/>
+      <c r="I30" s="3">
+        <f t="shared" si="3"/>
         <v>789</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="J30" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="4" t="s">
+      <c r="K30" s="16"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N30" s="6"/>
-      <c r="O30" s="9" t="s">
+      <c r="N30" s="17"/>
+      <c r="O30" s="5" t="s">
         <v>103</v>
       </c>
       <c r="P30" s="1" t="s">
@@ -2372,39 +2425,39 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="3" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
       <c r="E31" s="2">
         <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="3">
         <v>1.17</v>
       </c>
-      <c r="H31" s="7">
-        <f t="shared" si="2"/>
+      <c r="H31" s="3">
+        <f t="shared" si="4"/>
         <v>128.69999999999999</v>
       </c>
-      <c r="I31" s="15">
-        <f>H31*100</f>
+      <c r="I31" s="8">
+        <f t="shared" ref="I31:I37" si="5">H31*100</f>
         <v>12869.999999999998</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="4" t="s">
+      <c r="K31" s="16"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="6"/>
-      <c r="O31" s="9" t="s">
+      <c r="N31" s="17"/>
+      <c r="O31" s="5" t="s">
         <v>106</v>
       </c>
       <c r="P31" s="1" t="s">
@@ -2412,38 +2465,38 @@
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="12"/>
+      <c r="B32" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="3">
         <v>3.36</v>
       </c>
-      <c r="H32" s="7">
-        <f t="shared" si="2"/>
+      <c r="H32" s="3">
+        <f t="shared" si="4"/>
         <v>3.36</v>
       </c>
-      <c r="I32" s="7">
-        <f>H32*100</f>
+      <c r="I32" s="3">
+        <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="K32" s="5"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="N32" s="6"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="N32" s="17"/>
       <c r="O32" s="2" t="s">
         <v>117</v>
       </c>
@@ -2452,38 +2505,38 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="3" t="s">
+      <c r="A33" s="12"/>
+      <c r="B33" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
       <c r="E33" s="2">
         <v>2</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="3">
         <v>2.99</v>
       </c>
-      <c r="H33" s="7">
-        <f t="shared" si="2"/>
+      <c r="H33" s="3">
+        <f t="shared" si="4"/>
         <v>5.98</v>
       </c>
-      <c r="I33" s="7">
-        <f>H33*100</f>
+      <c r="I33" s="3">
+        <f t="shared" si="5"/>
         <v>598</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="K33" s="5"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="4" t="s">
+      <c r="K33" s="16"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="N33" s="6"/>
+      <c r="N33" s="17"/>
       <c r="O33" s="2" t="s">
         <v>117</v>
       </c>
@@ -2492,38 +2545,38 @@
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="12"/>
+      <c r="B34" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
       <c r="E34" s="2">
         <v>6</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="3">
         <v>3.14</v>
       </c>
-      <c r="H34" s="7">
-        <f t="shared" si="2"/>
+      <c r="H34" s="3">
+        <f t="shared" si="4"/>
         <v>18.84</v>
       </c>
-      <c r="I34" s="7">
-        <f>H34*100</f>
+      <c r="I34" s="3">
+        <f t="shared" si="5"/>
         <v>1884</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="K34" s="5"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="4" t="s">
+      <c r="K34" s="16"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="N34" s="17"/>
       <c r="O34" s="2" t="s">
         <v>117</v>
       </c>
@@ -2532,38 +2585,38 @@
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
       <c r="E35" s="2">
         <v>1</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="3">
         <v>3.79</v>
       </c>
-      <c r="H35" s="7">
-        <f t="shared" si="2"/>
+      <c r="H35" s="3">
+        <f t="shared" si="4"/>
         <v>3.79</v>
       </c>
-      <c r="I35" s="7">
-        <f>H35*100</f>
+      <c r="I35" s="3">
+        <f t="shared" si="5"/>
         <v>379</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="4" t="s">
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="N35" s="6"/>
+      <c r="N35" s="17"/>
       <c r="O35" s="2" t="s">
         <v>117</v>
       </c>
@@ -2572,41 +2625,41 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="3">
         <v>4.5</v>
       </c>
-      <c r="H36" s="7">
-        <f t="shared" si="2"/>
-        <v>60.75</v>
-      </c>
-      <c r="I36" s="7">
-        <f>H36*100</f>
-        <v>6075</v>
-      </c>
-      <c r="J36" s="4" t="s">
+      <c r="H36" s="3">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="5"/>
+        <v>6300</v>
+      </c>
+      <c r="J36" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="4" t="s">
+      <c r="K36" s="16"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="9" t="s">
+      <c r="N36" s="17"/>
+      <c r="O36" s="5" t="s">
         <v>125</v>
       </c>
       <c r="P36" s="1" t="s">
@@ -2614,763 +2667,789 @@
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
       <c r="E37" s="2">
         <v>72</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" s="7">
+        <v>136</v>
+      </c>
+      <c r="G37" s="3">
         <v>9.9600000000000009</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="3">
         <f>G37*3</f>
         <v>29.880000000000003</v>
       </c>
-      <c r="I37" s="7">
-        <f>H37*100</f>
+      <c r="I37" s="3">
+        <f t="shared" si="5"/>
         <v>2988.0000000000005</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="4" t="s">
+      <c r="J37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="16"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N37" s="17"/>
+      <c r="O37" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="P37" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
       <c r="E38" s="2">
         <v>72</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7">
-        <f t="shared" ref="I38:I56" si="3">H38*100</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="9"/>
+      <c r="F38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="3">
+        <v>9.99</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" ref="H38:H43" si="6">G38</f>
+        <v>9.99</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" ref="I38:I47" si="7">H38*100</f>
+        <v>999</v>
+      </c>
+      <c r="J38" s="15"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="N38" s="17"/>
+      <c r="O38" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="P38" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="3" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
       <c r="E39" s="2">
         <v>48</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G39" s="7">
+        <v>143</v>
+      </c>
+      <c r="G39" s="3">
         <v>11.71</v>
       </c>
-      <c r="H39" s="7">
-        <f>G39</f>
+      <c r="H39" s="3">
+        <f t="shared" si="6"/>
         <v>11.71</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="3">
         <f>H39*50</f>
         <v>585.5</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="K39" s="5"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N39" s="6"/>
-      <c r="O39" s="9" t="s">
+      <c r="J39" s="15" t="s">
         <v>142</v>
       </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N39" s="17"/>
+      <c r="O39" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="P39" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="3" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
       <c r="E40" s="2">
         <v>24</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G40" s="7">
+        <v>143</v>
+      </c>
+      <c r="G40" s="3">
         <v>11.91</v>
       </c>
-      <c r="H40" s="7">
-        <f>G40</f>
+      <c r="H40" s="3">
+        <f t="shared" si="6"/>
         <v>11.91</v>
       </c>
-      <c r="I40" s="7">
+      <c r="I40" s="3">
         <f>H40*25</f>
         <v>297.75</v>
       </c>
-      <c r="J40" s="4" t="s">
+      <c r="J40" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="K40" s="16"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N40" s="17"/>
+      <c r="O40" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="K40" s="5"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N40" s="6"/>
-      <c r="O40" s="9" t="s">
-        <v>146</v>
-      </c>
       <c r="P40" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="3" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
       <c r="E41" s="2">
         <f>28+12</f>
         <v>40</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G41" s="7">
+        <v>143</v>
+      </c>
+      <c r="G41" s="3">
         <v>20.440000000000001</v>
       </c>
-      <c r="H41" s="7">
-        <f>G41</f>
+      <c r="H41" s="3">
+        <f t="shared" si="6"/>
         <v>20.440000000000001</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="3">
         <f>H41*50</f>
         <v>1022.0000000000001</v>
       </c>
-      <c r="J41" s="4" t="s">
+      <c r="J41" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K41" s="16"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N41" s="17"/>
+      <c r="O41" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N41" s="6"/>
-      <c r="O41" s="9" t="s">
-        <v>156</v>
-      </c>
       <c r="P41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
       <c r="E42" s="2">
         <v>4</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G42" s="7">
+        <v>136</v>
+      </c>
+      <c r="G42" s="3">
         <v>6.67</v>
       </c>
-      <c r="H42" s="7">
-        <f>G42</f>
+      <c r="H42" s="3">
+        <f t="shared" si="6"/>
         <v>6.67</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="3">
         <f>H42*20</f>
         <v>133.4</v>
       </c>
-      <c r="J42" s="4" t="s">
+      <c r="J42" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" s="16"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N42" s="17"/>
+      <c r="O42" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N42" s="6"/>
-      <c r="O42" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="P42" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
       <c r="E43" s="2">
         <v>4</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G43" s="7">
+        <v>143</v>
+      </c>
+      <c r="G43" s="3">
         <v>6.9</v>
       </c>
-      <c r="H43" s="7">
-        <f>G43</f>
+      <c r="H43" s="3">
+        <f t="shared" si="6"/>
         <v>6.9</v>
       </c>
-      <c r="I43" s="7">
+      <c r="I43" s="3">
         <f>H43*5</f>
         <v>34.5</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N43" s="6"/>
-      <c r="O43" s="9" t="s">
+      <c r="J43" s="15" t="s">
         <v>151</v>
       </c>
+      <c r="K43" s="16"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N43" s="17"/>
+      <c r="O43" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="P43" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
       <c r="E44" s="2">
         <v>24</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="10"/>
+      <c r="G44" s="3">
+        <v>28.44</v>
+      </c>
+      <c r="H44" s="3">
+        <f>G44*E44</f>
+        <v>682.56000000000006</v>
+      </c>
+      <c r="I44" s="8">
+        <f>H44*100</f>
+        <v>68256</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="N44" s="17"/>
+      <c r="O44" s="5" t="s">
+        <v>180</v>
+      </c>
       <c r="P44" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="22"/>
+      <c r="B45" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="2">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
+        <f>G45*E45</f>
+        <v>60</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="7"/>
+        <v>6000</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="N45" s="17"/>
+      <c r="O45" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="22"/>
+      <c r="B46" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="2">
-        <v>12</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="4"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
       <c r="E46" s="2">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="3">
         <v>122.99</v>
       </c>
-      <c r="H46" s="7">
-        <f>G46</f>
+      <c r="H46" s="3">
+        <f t="shared" ref="H46:H51" si="8">G46</f>
         <v>122.99</v>
       </c>
-      <c r="I46" s="15">
-        <f t="shared" si="3"/>
+      <c r="I46" s="8">
+        <f t="shared" si="7"/>
         <v>12299</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="4" t="s">
+      <c r="J46" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="K46" s="16"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="N46" s="6"/>
-      <c r="O46" s="10" t="s">
-        <v>166</v>
+      <c r="N46" s="17"/>
+      <c r="O46" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="2">
+        <v>324</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="3">
+        <v>15.99</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="8"/>
+        <v>15.99</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="7"/>
+        <v>1599</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K47" s="16"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="N47" s="17"/>
+      <c r="O47" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="22"/>
+      <c r="B48" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G47" s="7">
-        <v>15.99</v>
-      </c>
-      <c r="H47" s="7">
-        <f>G47</f>
-        <v>15.99</v>
-      </c>
-      <c r="I47" s="7">
-        <f t="shared" si="3"/>
-        <v>1599</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="N47" s="6"/>
-      <c r="O47" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
       <c r="E48" s="2">
         <v>24</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G48" s="7">
+        <v>143</v>
+      </c>
+      <c r="G48" s="3">
         <v>16.79</v>
       </c>
-      <c r="H48" s="7">
-        <f>G48</f>
+      <c r="H48" s="3">
+        <f t="shared" si="8"/>
         <v>16.79</v>
       </c>
-      <c r="I48" s="7">
+      <c r="I48" s="3">
         <f>H48*24</f>
         <v>402.96</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N48" s="6"/>
-      <c r="O48" s="9" t="s">
+      <c r="J48" s="15" t="s">
         <v>147</v>
       </c>
+      <c r="K48" s="16"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N48" s="17"/>
+      <c r="O48" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="P48" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
       <c r="E49" s="2">
         <v>24</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G49" s="7">
+        <v>149</v>
+      </c>
+      <c r="G49" s="3">
         <v>7.35</v>
       </c>
-      <c r="H49" s="7">
-        <f>G49</f>
+      <c r="H49" s="3">
+        <f t="shared" si="8"/>
         <v>7.35</v>
       </c>
-      <c r="I49" s="7">
+      <c r="I49" s="3">
         <f>H49*50</f>
         <v>367.5</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="N49" s="6"/>
-      <c r="O49" s="9" t="s">
-        <v>168</v>
+      <c r="J49" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="K49" s="16"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N49" s="17"/>
+      <c r="O49" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
       <c r="E50" s="2">
         <v>3.5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G50" s="7">
+        <v>163</v>
+      </c>
+      <c r="G50" s="3">
         <v>9.49</v>
       </c>
-      <c r="H50" s="7">
-        <f>G50</f>
+      <c r="H50" s="3">
+        <f t="shared" si="8"/>
         <v>9.49</v>
       </c>
-      <c r="I50" s="7">
+      <c r="I50" s="3">
         <f>H50*6</f>
         <v>56.94</v>
       </c>
-      <c r="J50" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="4" t="s">
+      <c r="J50" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="K50" s="16"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="N50" s="6"/>
-      <c r="O50" s="10" t="s">
-        <v>163</v>
+      <c r="N50" s="17"/>
+      <c r="O50" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="18"/>
-      <c r="B51" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
       <c r="E51" s="2">
         <v>3</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="7">
+        <v>170</v>
+      </c>
+      <c r="G51" s="3">
         <v>364.86</v>
       </c>
-      <c r="H51" s="7">
-        <f>G51</f>
+      <c r="H51" s="3">
+        <f t="shared" si="8"/>
         <v>364.86</v>
       </c>
-      <c r="I51" s="7">
+      <c r="I51" s="3">
         <f>H51</f>
         <v>364.86</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="4" t="s">
+      <c r="J51" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K51" s="16"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="N51" s="6"/>
-      <c r="O51" s="9" t="s">
+      <c r="N51" s="17"/>
+      <c r="O51" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="2">
+        <v>174</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="3">
+        <v>50</v>
+      </c>
+      <c r="H52" s="10">
+        <f>G52*E52</f>
+        <v>8700</v>
+      </c>
+      <c r="I52" s="3">
+        <f>H52</f>
+        <v>8700</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K52" s="16"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="N52" s="17"/>
+      <c r="O52" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="2">
-        <v>152</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G52" s="7">
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="2">
+        <v>66</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" s="3">
         <v>50</v>
       </c>
-      <c r="H52" s="20">
-        <f>G52*E52</f>
-        <v>7600</v>
-      </c>
-      <c r="I52" s="7">
-        <f>H52</f>
-        <v>7600</v>
-      </c>
-      <c r="J52" s="4" t="s">
+      <c r="H53" s="10">
+        <f t="shared" ref="H53:H55" si="9">G53*E53</f>
+        <v>3300</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" ref="I53:I55" si="10">H53</f>
+        <v>3300</v>
+      </c>
+      <c r="J53" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="K52" s="5"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="4" t="s">
+      <c r="K53" s="16"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="N52" s="6"/>
-      <c r="O52" s="10" t="s">
+      <c r="N53" s="17"/>
+      <c r="O53" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="3" t="s">
+      <c r="P53" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="2">
-        <v>100</v>
-      </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="7">
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="2">
+        <v>84</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="3">
         <v>50</v>
       </c>
-      <c r="H53" s="20">
-        <f t="shared" ref="H53:H55" si="4">G53*E53</f>
-        <v>5000</v>
-      </c>
-      <c r="I53" s="7">
-        <f t="shared" ref="I53:I55" si="5">H53</f>
-        <v>5000</v>
-      </c>
-      <c r="J53" s="4" t="s">
+      <c r="H54" s="10">
+        <f t="shared" si="9"/>
+        <v>4200</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="10"/>
+        <v>4200</v>
+      </c>
+      <c r="J54" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="K53" s="5"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="4" t="s">
+      <c r="K54" s="16"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="N53" s="6"/>
-      <c r="O53" s="10" t="s">
+      <c r="N54" s="17"/>
+      <c r="O54" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="3" t="s">
+      <c r="P54" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="2">
-        <v>100</v>
-      </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="7">
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="2">
+        <v>104</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G55" s="3">
         <v>50</v>
       </c>
-      <c r="H54" s="20">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-      <c r="I54" s="7">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-      <c r="J54" s="4" t="s">
+      <c r="H55" s="10">
+        <f t="shared" si="9"/>
+        <v>5200</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="10"/>
+        <v>5200</v>
+      </c>
+      <c r="J55" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="K54" s="5"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="4" t="s">
+      <c r="K55" s="16"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="N54" s="6"/>
-      <c r="O54" s="10" t="s">
+      <c r="N55" s="17"/>
+      <c r="O55" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="2">
-        <v>100</v>
-      </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="7">
-        <v>50</v>
-      </c>
-      <c r="H55" s="20">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-      <c r="I55" s="7">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K55" s="5"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="N55" s="6"/>
-      <c r="O55" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="P55" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="10"/>
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
       <c r="P56" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="172">
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="J54:L54"/>
-    <mergeCell ref="M54:N54"/>
+  <mergeCells count="168">
+    <mergeCell ref="A52:A55"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="J51:L51"/>
     <mergeCell ref="M51:N51"/>
@@ -3383,6 +3462,25 @@
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="J50:L50"/>
     <mergeCell ref="M50:N50"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A36:A51"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="M37:N37"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="J47:L47"/>
     <mergeCell ref="M47:N47"/>
@@ -3401,7 +3499,6 @@
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="J44:L44"/>
     <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A2:A35"/>
     <mergeCell ref="S23:T23"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="J41:L41"/>
@@ -3409,16 +3506,6 @@
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A36:A51"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="M37:N37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J38:L38"/>
     <mergeCell ref="M38:N38"/>
@@ -3428,6 +3515,10 @@
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="M33:N33"/>
@@ -3440,15 +3531,25 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="J29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B28:D28"/>
@@ -3466,18 +3567,6 @@
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="M17:N17"/>
     <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M6:N6"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="J24:L24"/>
@@ -3485,41 +3574,35 @@
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="J27:L27"/>
     <mergeCell ref="J16:L16"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="J18:L18"/>
     <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B4:D4"/>
@@ -3530,6 +3613,10 @@
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -3574,7 +3661,1540 @@
     <hyperlink ref="O47" r:id="rId39" display="https://www.amazon.com/SUNLU-Printer-Filament-Dimensional-Clear/dp/B0C3J1X41K/ref=sr_1_3?crid=1BF4C1AVVVY7C&amp;dib=eyJ2IjoiMSJ9.uHO_RtwANQlBn3JFBGzMz6yLSKkCiyms4KGRLjWbiEagAVCCQ_8TvtLDb82fJtvj-x1KzB_EOAZWDwSrN9MeaBNOUz7G4iZUkzUNhATqWjaG-poMpEajUeJfe8KPZMrffqaFCdjRZS_Xjq-sCnZzU9sWMIzPoHzjgFmpRhugbrsY0U-nkdxETIaDoKiS328mH4CxsC41QfBRqLhl2N_krrwMRaTOGlcN8B2R8gZiA8Q.KyZp65f3fsAqrUWuYANhgbrDXv_W8jqW9DbxSCrzvBE&amp;dib_tag=se&amp;keywords=transparent%2Borange%2B1.75mm&amp;qid=1765862903&amp;sprefix=transparent%2Borange%2B1.75mm%2B%2Caps%2C127&amp;sr=8-3&amp;th=1" xr:uid="{1A860C3B-8705-4CB7-A458-75F27794B65F}"/>
     <hyperlink ref="O49" r:id="rId40" xr:uid="{36D6A204-29CC-496A-AA9D-E59534869F95}"/>
     <hyperlink ref="O51" r:id="rId41" xr:uid="{F92F3D5B-C987-429A-9A61-8F4EE2728279}"/>
+    <hyperlink ref="O45" r:id="rId42" xr:uid="{8C9C17B2-FFD0-4424-B973-040410501A83}"/>
+    <hyperlink ref="O44" r:id="rId43" xr:uid="{7D1E339D-72D7-4B02-9CD0-9399ACFC68BA}"/>
+    <hyperlink ref="O38" r:id="rId44" display="https://www.amazon.com/Yaocom-European-Standard-Aluminum-Extrusion/dp/B0DX7B5ZNN/ref=sr_1_3?dib=eyJ2IjoiMSJ9.dnPBW5BnGWFI7alZa4I2U-eVIo5GXTpxHJ9tQMCOqZxXMZPrh3lK9sBZdB6eNKI7a_ZoQK8DljT8j86EjeJB-TgIjBv-7rR1aWPd3Za75LvZ6xV36SRWb3nkD_9LcJV4SBCgqPJvykjxeW4zMrXNekWu9XvrzbX6PY3tsirpeNhu1zFpZ2WD0UqR3vN_whM5FQffhRQ2tPdUu8WPP_oVwzEKxtiEkEmALW8h0yRnwVY.X_WCrDJoZ7GpA7NadGh_qshU4Mp-sX0PWu2dVc1ia4c&amp;dib_tag=se&amp;keywords=m5%2B2020%2Bnut&amp;qid=1766005804&amp;sr=8-3&amp;th=1" xr:uid="{76E4D916-016C-41F3-AC21-753F29DBF30F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId45"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57266FC2-9302-4B96-8DEA-F758E4D39AA9}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="C2" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="3">
+        <f t="shared" ref="J2:J14" si="0">I2*G2</f>
+        <v>5.4</v>
+      </c>
+      <c r="K2" s="3">
+        <f t="shared" ref="K2:K33" si="1">J2*100</f>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="2">
+        <v>37</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="J3" s="3">
+        <f t="shared" si="0"/>
+        <v>33.67</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" si="1"/>
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C4" s="24"/>
+      <c r="D4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2.83</v>
+      </c>
+      <c r="J4" s="3">
+        <f t="shared" si="0"/>
+        <v>11.32</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="1"/>
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C5" s="24"/>
+      <c r="D5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="2">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="0"/>
+        <v>8.16</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="1"/>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="24"/>
+      <c r="D6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="2">
+        <v>4</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="0"/>
+        <v>19.920000000000002</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="1"/>
+        <v>1992.0000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C7" s="24"/>
+      <c r="D7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="2">
+        <v>53</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.67</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>88.509999999999991</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="1"/>
+        <v>8851</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C8" s="24"/>
+      <c r="D8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="2">
+        <v>12</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="0"/>
+        <v>3.96</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="1"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C9" s="24"/>
+      <c r="D9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="2">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" si="0"/>
+        <v>15.64</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="1"/>
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C10" s="24"/>
+      <c r="D10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="2">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="0"/>
+        <v>51.66</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="1"/>
+        <v>5166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C11" s="24"/>
+      <c r="D11" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="2">
+        <v>12</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="0"/>
+        <v>6.48</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="1"/>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C12" s="24"/>
+      <c r="D12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="2">
+        <v>188</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="0"/>
+        <v>18.8</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C13" s="24"/>
+      <c r="D13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="2">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="0"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="1"/>
+        <v>240.00000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C14" s="24"/>
+      <c r="D14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.86999999999999988</v>
+      </c>
+      <c r="K14" s="3">
+        <f t="shared" si="1"/>
+        <v>86.999999999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C15" s="24"/>
+      <c r="D15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="2">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4.51</v>
+      </c>
+      <c r="J15" s="3">
+        <f>I15</f>
+        <v>4.51</v>
+      </c>
+      <c r="K15" s="3">
+        <f t="shared" si="1"/>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C16" s="24"/>
+      <c r="D16" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="2">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5.87</v>
+      </c>
+      <c r="J16" s="3">
+        <f>I16*G16</f>
+        <v>46.96</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="1"/>
+        <v>4696</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C17" s="24"/>
+      <c r="D17" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="J17" s="3">
+        <f>I17*G17</f>
+        <v>1.6500000000000001</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C18" s="24"/>
+      <c r="D18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4.28</v>
+      </c>
+      <c r="J18" s="3">
+        <f>I18*G18</f>
+        <v>17.12</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="24"/>
+      <c r="D19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="2">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="J19" s="3">
+        <f>I19*G19</f>
+        <v>12</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" s="24"/>
+      <c r="D20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" ref="J20:J33" si="2">I20*G20</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="1"/>
+        <v>243.00000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21" s="24"/>
+      <c r="D21" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="2">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J21" s="3">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="1"/>
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="24"/>
+      <c r="D22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="2"/>
+        <v>1.96</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="1"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C23" s="24"/>
+      <c r="D23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="K23" s="3">
+        <f t="shared" si="1"/>
+        <v>252.99999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="24"/>
+      <c r="D24" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="2">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="K24" s="3">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="24"/>
+      <c r="D25" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="2">
+        <v>2</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.35</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="2"/>
+        <v>4.7</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" si="1"/>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C26" s="24"/>
+      <c r="D26" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="2">
+        <v>3</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="2"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="24"/>
+      <c r="D27" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0.59</v>
+      </c>
+      <c r="J27" s="3">
+        <f t="shared" si="2"/>
+        <v>1.18</v>
+      </c>
+      <c r="K27" s="3">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" s="24"/>
+      <c r="D28" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.45</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="2"/>
+        <v>3.45</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" si="1"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C29" s="24"/>
+      <c r="D29" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="2">
+        <v>6</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J29" s="3">
+        <f t="shared" si="2"/>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="K29" s="3">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="24"/>
+      <c r="D30" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="J30" s="3">
+        <f t="shared" si="2"/>
+        <v>7.89</v>
+      </c>
+      <c r="K30" s="3">
+        <f t="shared" si="1"/>
+        <v>789</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="24"/>
+      <c r="D31" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="2">
+        <v>110</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="J31" s="3">
+        <f t="shared" si="2"/>
+        <v>128.69999999999999</v>
+      </c>
+      <c r="K31" s="8">
+        <f t="shared" si="1"/>
+        <v>12869.999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="24"/>
+      <c r="D32" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="J32" s="3">
+        <f t="shared" si="2"/>
+        <v>3.36</v>
+      </c>
+      <c r="K32" s="3">
+        <f t="shared" si="1"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C33" s="24"/>
+      <c r="D33" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="2">
+        <v>2</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="J33" s="3">
+        <f t="shared" si="2"/>
+        <v>5.98</v>
+      </c>
+      <c r="K33" s="3">
+        <f t="shared" si="1"/>
+        <v>598</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="C2:C33"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42ADF804-9B81-4207-8124-1363A484F869}">
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C7" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="2">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" ref="J7:J9" si="0">I7*G7</f>
+        <v>18.84</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" ref="K7:K20" si="1">J7*100</f>
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3.79</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="0"/>
+        <v>3.79</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="1"/>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C9" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="2">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="1"/>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C10" s="27"/>
+      <c r="D10" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="2">
+        <v>72</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="J10" s="3">
+        <f>I10*3</f>
+        <v>29.880000000000003</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="1"/>
+        <v>2988.0000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C11" s="27"/>
+      <c r="D11" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="2">
+        <v>72</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="3">
+        <v>9.99</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" ref="J11:J16" si="2">I11</f>
+        <v>9.99</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="1"/>
+        <v>999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C12" s="27"/>
+      <c r="D12" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="2">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" s="3">
+        <v>11.71</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="2"/>
+        <v>11.71</v>
+      </c>
+      <c r="K12" s="3">
+        <f>J12*50</f>
+        <v>585.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C13" s="27"/>
+      <c r="D13" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="2">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="3">
+        <v>11.91</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="2"/>
+        <v>11.91</v>
+      </c>
+      <c r="K13" s="3">
+        <f>J13*25</f>
+        <v>297.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C14" s="27"/>
+      <c r="D14" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="2">
+        <f>28+12</f>
+        <v>40</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="3">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="J14" s="3">
+        <f t="shared" si="2"/>
+        <v>20.440000000000001</v>
+      </c>
+      <c r="K14" s="3">
+        <f>J14*50</f>
+        <v>1022.0000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C15" s="27"/>
+      <c r="D15" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6.67</v>
+      </c>
+      <c r="J15" s="3">
+        <f t="shared" si="2"/>
+        <v>6.67</v>
+      </c>
+      <c r="K15" s="3">
+        <f>J15*20</f>
+        <v>133.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C16" s="27"/>
+      <c r="D16" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I16" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" si="2"/>
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="3">
+        <f>J16*5</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C17" s="27"/>
+      <c r="D17" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="2">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="3">
+        <v>28.44</v>
+      </c>
+      <c r="J17" s="3">
+        <f>I17*G17</f>
+        <v>682.56000000000006</v>
+      </c>
+      <c r="K17" s="8">
+        <f>J17*100</f>
+        <v>68256</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C18" s="27"/>
+      <c r="D18" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="2">
+        <v>12</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="3">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <f>I18*G18</f>
+        <v>60</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="27"/>
+      <c r="D19" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="3">
+        <v>122.99</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" ref="J19:J24" si="3">I19</f>
+        <v>122.99</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="1"/>
+        <v>12299</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" s="27"/>
+      <c r="D20" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="2">
+        <v>324</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="3">
+        <v>15.99</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" si="3"/>
+        <v>15.99</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="1"/>
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21" s="27"/>
+      <c r="D21" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="2">
+        <v>24</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21" s="3">
+        <v>16.79</v>
+      </c>
+      <c r="J21" s="3">
+        <f t="shared" si="3"/>
+        <v>16.79</v>
+      </c>
+      <c r="K21" s="3">
+        <f>J21*24</f>
+        <v>402.96</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="27"/>
+      <c r="D22" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="2">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="3"/>
+        <v>7.35</v>
+      </c>
+      <c r="K22" s="3">
+        <f>J22*50</f>
+        <v>367.5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C23" s="27"/>
+      <c r="D23" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="3">
+        <v>9.49</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="3"/>
+        <v>9.49</v>
+      </c>
+      <c r="K23" s="3">
+        <f>J23*6</f>
+        <v>56.94</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="28"/>
+      <c r="D24" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="2">
+        <v>3</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="3">
+        <v>364.86</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="3"/>
+        <v>364.86</v>
+      </c>
+      <c r="K24" s="3">
+        <f>J24</f>
+        <v>364.86</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="2">
+        <v>174</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="3">
+        <v>50</v>
+      </c>
+      <c r="J25" s="10">
+        <f>I25*G25</f>
+        <v>8700</v>
+      </c>
+      <c r="K25" s="3">
+        <f>J25</f>
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C26" s="24"/>
+      <c r="D26" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="2">
+        <v>66</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I26" s="3">
+        <v>50</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" ref="J26:J28" si="4">I26*G26</f>
+        <v>3300</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" ref="K26:K28" si="5">J26</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="24"/>
+      <c r="D27" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="2">
+        <v>84</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="3">
+        <v>50</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="4"/>
+        <v>4200</v>
+      </c>
+      <c r="K27" s="3">
+        <f t="shared" si="5"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" s="24"/>
+      <c r="D28" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="2">
+        <v>104</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I28" s="3">
+        <v>50</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="4"/>
+        <v>5200</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" si="5"/>
+        <v>5200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="C9:C24"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>